--- a/e2e/expectedData/moju_BFKJ_Q1.xlsx
+++ b/e2e/expectedData/moju_BFKJ_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>DAFTAR PEMBAYARAN KARYAWAN</t>
   </si>
@@ -50,7 +50,7 @@
     <t>BFKJ - Expat (Jan)</t>
   </si>
   <si>
-    <t>1,850.00</t>
+    <t>1,200.00</t>
   </si>
   <si>
     <t>BFKJ - Local (Feb)</t>
@@ -71,9 +71,6 @@
     <t>BDD BFKJ - Expat (Mar)</t>
   </si>
   <si>
-    <t>1,300.00</t>
-  </si>
-  <si>
     <t>BDD BFKJ - Local (Apr)</t>
   </si>
   <si>
@@ -179,10 +176,10 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>6,850.00</t>
-  </si>
-  <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>6,800.00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -687,7 +684,9 @@
       <c r="C6" s="3">
         <v>11804051</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>650.0</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5">
@@ -730,7 +729,9 @@
       <c r="C9" s="3">
         <v>11804052</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>650.0</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
@@ -773,7 +774,9 @@
       <c r="C12" s="3">
         <v>11804052</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>650.0</v>
+      </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5">
@@ -799,8 +802,8 @@
       <c r="C14" s="3">
         <v>11804052</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
+      <c r="D14" s="4">
+        <v>650.0</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -809,7 +812,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3">
         <v>11804052</v>
@@ -822,7 +825,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3">
         <v>11804052</v>
@@ -835,7 +838,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3">
         <v>11804052</v>
@@ -848,7 +851,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3">
         <v>11804052</v>
@@ -861,7 +864,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3">
         <v>11804052</v>
@@ -874,7 +877,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3">
         <v>11804052</v>
@@ -887,7 +890,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3">
         <v>11804052</v>
@@ -900,7 +903,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3">
         <v>11804052</v>
@@ -913,7 +916,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3">
         <v>11804052</v>
@@ -926,7 +929,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
         <v>11804052</v>
@@ -939,7 +942,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
         <v>11804052</v>
@@ -952,7 +955,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="3">
         <v>11804052</v>
@@ -965,7 +968,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3">
         <v>11804052</v>
@@ -978,7 +981,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3">
         <v>11804052</v>
@@ -991,7 +994,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="3">
         <v>11804052</v>
@@ -1004,7 +1007,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="3">
         <v>11804052</v>
@@ -1017,7 +1020,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="3">
         <v>11804052</v>
@@ -1030,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3">
         <v>11804052</v>
@@ -1043,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="3">
         <v>11804052</v>
@@ -1056,7 +1059,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3">
         <v>11804052</v>
@@ -1069,7 +1072,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3">
         <v>11804052</v>
@@ -1082,7 +1085,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3">
         <v>11804052</v>
@@ -1095,7 +1098,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="3">
         <v>11804052</v>
@@ -1108,7 +1111,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3">
         <v>11804052</v>
@@ -1121,7 +1124,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="3">
         <v>11804052</v>
@@ -1134,7 +1137,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="3">
         <v>11804052</v>
@@ -1147,7 +1150,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="3">
         <v>11804052</v>
@@ -1160,7 +1163,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="3">
         <v>51114007</v>
@@ -1175,13 +1178,13 @@
         <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="3">
         <v>51114007</v>
       </c>
       <c r="D43" s="4">
-        <v>440.0</v>
+        <v>275.0</v>
       </c>
       <c r="E43" s="4"/>
     </row>
@@ -1190,12 +1193,14 @@
         <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="3">
         <v>51114007</v>
       </c>
-      <c r="D44" s="4"/>
+      <c r="D44" s="4">
+        <v>115.0</v>
+      </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5">
@@ -1203,14 +1208,14 @@
         <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="3">
         <v>20501024</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4">
-        <v>550.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1218,32 +1223,32 @@
         <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49"/>
       <c r="C49"/>
@@ -1252,23 +1257,23 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50"/>
       <c r="D50" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51"/>
       <c r="D51" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" s="7"/>
     </row>
@@ -1281,23 +1286,23 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53"/>
       <c r="D53" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E53" s="7"/>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54"/>
       <c r="D54" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E54" s="7"/>
     </row>

--- a/e2e/expectedData/moju_BFKJ_Q1.xlsx
+++ b/e2e/expectedData/moju_BFKJ_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>DAFTAR PEMBAYARAN KARYAWAN</t>
   </si>
@@ -50,9 +50,6 @@
     <t>BFKJ - Expat (Jan)</t>
   </si>
   <si>
-    <t>1,200.00</t>
-  </si>
-  <si>
     <t>BFKJ - Local (Feb)</t>
   </si>
   <si>
@@ -170,16 +167,16 @@
     <t>TL20000002</t>
   </si>
   <si>
-    <t>6,300.00</t>
+    <t>5,200.00</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>6,800.00</t>
-  </si>
-  <si>
-    <t>DILI, 09 September 2026</t>
+    <t>5,590.00</t>
+  </si>
+  <si>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -714,8 +711,8 @@
       <c r="C8" s="3">
         <v>11804052</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>11</v>
+      <c r="D8" s="4">
+        <v>650.0</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -724,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>11804052</v>
@@ -739,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
         <v>11804052</v>
@@ -754,13 +751,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
         <v>11804052</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
+      <c r="D11" s="4">
+        <v>650.0</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -769,7 +766,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
         <v>11804052</v>
@@ -784,7 +781,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3">
         <v>11804052</v>
@@ -797,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3">
         <v>11804052</v>
@@ -812,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3">
         <v>11804052</v>
@@ -825,7 +822,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3">
         <v>11804052</v>
@@ -838,7 +835,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3">
         <v>11804052</v>
@@ -851,7 +848,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3">
         <v>11804052</v>
@@ -864,7 +861,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3">
         <v>11804052</v>
@@ -877,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3">
         <v>11804052</v>
@@ -890,7 +887,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3">
         <v>11804052</v>
@@ -903,7 +900,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3">
         <v>11804052</v>
@@ -916,7 +913,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="3">
         <v>11804052</v>
@@ -929,7 +926,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3">
         <v>11804052</v>
@@ -942,7 +939,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3">
         <v>11804052</v>
@@ -955,7 +952,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="3">
         <v>11804052</v>
@@ -968,7 +965,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3">
         <v>11804052</v>
@@ -981,7 +978,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3">
         <v>11804052</v>
@@ -994,7 +991,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="3">
         <v>11804052</v>
@@ -1007,7 +1004,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="3">
         <v>11804052</v>
@@ -1020,7 +1017,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="3">
         <v>11804052</v>
@@ -1033,7 +1030,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="3">
         <v>11804052</v>
@@ -1046,7 +1043,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="3">
         <v>11804052</v>
@@ -1059,7 +1056,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="3">
         <v>11804052</v>
@@ -1072,7 +1069,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3">
         <v>11804052</v>
@@ -1085,7 +1082,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="3">
         <v>11804052</v>
@@ -1098,7 +1095,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="3">
         <v>11804052</v>
@@ -1111,7 +1108,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="3">
         <v>11804052</v>
@@ -1124,7 +1121,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3">
         <v>11804052</v>
@@ -1137,7 +1134,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="3">
         <v>11804052</v>
@@ -1150,7 +1147,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="3">
         <v>11804052</v>
@@ -1163,7 +1160,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42" s="3">
         <v>51114007</v>
@@ -1178,13 +1175,13 @@
         <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="3">
         <v>51114007</v>
       </c>
       <c r="D43" s="4">
-        <v>275.0</v>
+        <v>165.0</v>
       </c>
       <c r="E43" s="4"/>
     </row>
@@ -1193,7 +1190,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="3">
         <v>51114007</v>
@@ -1208,14 +1205,14 @@
         <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="3">
         <v>20501024</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4">
-        <v>500.0</v>
+        <v>390.0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1223,32 +1220,32 @@
         <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49"/>
       <c r="C49"/>
@@ -1257,23 +1254,23 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50"/>
       <c r="D50" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51"/>
       <c r="D51" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51" s="7"/>
     </row>
@@ -1286,23 +1283,23 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53"/>
       <c r="D53" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53" s="7"/>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54"/>
       <c r="D54" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E54" s="7"/>
     </row>
